--- a/public/bulk-listing-templates/IERADA_Bulk_Listing_Single_Products.xlsx
+++ b/public/bulk-listing-templates/IERADA_Bulk_Listing_Single_Products.xlsx
@@ -23,7 +23,7 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>Admin Size attributes. Pick from the dropdown. Multiple sizes: 6, 7, 8.</t>
+          <t>One size per row. Kids Fashion uses age-group sizes (6-9 Months, 2-2.5 Years), not adult S/M/L.</t>
         </r>
       </text>
     </comment>
@@ -40,7 +40,7 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>Admin Size attributes. Pick from the dropdown. Multiple sizes: 6, 7, 8.</t>
+          <t>One size per row. Kids Fashion uses age-group sizes (6-9 Months, 2-2.5 Years), not adult S/M/L.</t>
         </r>
       </text>
     </comment>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="270">
   <si>
     <t>IERADA Seller Panel</t>
   </si>
@@ -129,13 +129,22 @@
     <t>On Step 4, download Completed listing.xlsx, edit any cell, re-upload on the same Preview step, then submit. Images are not restaged unless the SKU changed.</t>
   </si>
   <si>
+    <t>One SKU, one colour, one size</t>
+  </si>
+  <si>
+    <t>Each Products row is one listing. Write one SKU, one colour and one size only.</t>
+  </si>
+  <si>
+    <t>Do not put comma-separated colours or sizes in the same cell. If the product has more than one colour or size, download the Colour × Size Variations template instead.</t>
+  </si>
+  <si>
     <t>Size dropdown (admin Size attributes)</t>
   </si>
   <si>
-    <t>The Size column is a dropdown of live admin Size attributes. Open the cell and pick a size.</t>
-  </si>
-  <si>
-    <t>Multiple sizes go in the same Size cell, separated by comma (example: 6, 7, 8). Names must match the dropdown. The wizard lists one SKU per size and keeps the original image mapping.</t>
+    <t>The Size column is a dropdown of live admin Size attributes. Open the cell and pick one size.</t>
+  </si>
+  <si>
+    <t>Kids Fashion: choose an age-group size so buyers understand the fit — 6-9 Months, 9-12 Months, 12-15 Months, 18-21 Months, 2-2.5 Years, 3-3.5 Years, 5-5.5 Years. Do not use adult S/M/L for kids apparel.</t>
   </si>
   <si>
     <t>Image mapping for single products</t>
@@ -165,7 +174,7 @@
     <t>sku</t>
   </si>
   <si>
-    <t>Unique seller SKU. Image files must start with this value plus -{n}.</t>
+    <t>One unique seller SKU per product row. Image files must start with this value plus -{n}.</t>
   </si>
   <si>
     <t>Brand Type</t>
@@ -192,7 +201,7 @@
     <t>colour</t>
   </si>
   <si>
-    <t>Catalogue colour name. Required to publish a single listing.</t>
+    <t>One catalogue colour only. Do not write comma-separated colours. Use the Colour × Size template for more than one colour.</t>
   </si>
   <si>
     <t>Size</t>
@@ -201,7 +210,7 @@
     <t>size</t>
   </si>
   <si>
-    <t>Pick from the Size dropdown (admin Size attributes). Multiple sizes in the same cell: 6, 7, 8.</t>
+    <t>One size only. Pick from the Size dropdown. Kids Fashion: choose an age-group size (6-9 Months, 2-2.5 Years). Use Colour × Size for more than one size.</t>
   </si>
   <si>
     <t>MRP ₹</t>
@@ -519,70 +528,193 @@
     <t>• ZIP folders are flattened. Nested folders are allowed; only the file name is used for SKU matching.</t>
   </si>
   <si>
-    <t>Free Size</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>12-15 Months</t>
+  </si>
+  <si>
+    <t>15-18 Months</t>
+  </si>
+  <si>
+    <t>18-21 Months</t>
+  </si>
+  <si>
+    <t>2-2.5 Years</t>
+  </si>
+  <si>
+    <t>2.5-3 Years</t>
+  </si>
+  <si>
+    <t>21-24 Months</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>3-3.5 Years</t>
+  </si>
+  <si>
+    <t>3.5-4 Years</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>3XL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4-4.5 Years</t>
+  </si>
+  <si>
+    <t>4.5-5 Years</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>4XL</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>5-5.5 Years</t>
+  </si>
+  <si>
+    <t>5.5-6 Years</t>
+  </si>
+  <si>
+    <t>5XL</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>6 Month</t>
+  </si>
+  <si>
+    <t>6-9 Months</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>8 Months</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>9-12 Months</t>
+  </si>
+  <si>
+    <t>Beetroot</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>Free size</t>
+  </si>
+  <si>
+    <t>IND-1</t>
+  </si>
+  <si>
+    <t>IND-10</t>
+  </si>
+  <si>
+    <t>IND-11</t>
+  </si>
+  <si>
+    <t>IND-12</t>
+  </si>
+  <si>
+    <t>IND-13</t>
+  </si>
+  <si>
+    <t>IND-2</t>
+  </si>
+  <si>
+    <t>IND-3</t>
+  </si>
+  <si>
+    <t>IND-4</t>
+  </si>
+  <si>
+    <t>IND-5</t>
+  </si>
+  <si>
+    <t>IND-6</t>
+  </si>
+  <si>
+    <t>IND-7</t>
+  </si>
+  <si>
+    <t>IND-8</t>
+  </si>
+  <si>
+    <t>IND-9</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>XL</t>
   </si>
   <si>
     <t>XS</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
     <t>XXL</t>
   </si>
   <si>
-    <t>3XL</t>
-  </si>
-  <si>
-    <t>4XL</t>
-  </si>
-  <si>
-    <t>5XL</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>IND-6</t>
-  </si>
-  <si>
-    <t>IND-7</t>
-  </si>
-  <si>
-    <t>IND-8</t>
-  </si>
-  <si>
-    <t>IND-9</t>
-  </si>
-  <si>
-    <t>IND-10</t>
+    <t>XXXL</t>
   </si>
   <si>
     <t>Generic</t>
@@ -1332,7 +1464,7 @@
   <sheetPr>
     <tabColor rgb="FFF56C43"/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1520,516 +1652,537 @@
       <c r="C27" s="13"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+    </row>
+    <row r="31" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B34" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C34" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+    <row r="35" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B35" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C35" s="18" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>57</v>
+      <c r="A38" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>60</v>
+      <c r="A39" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="C45" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="B46" s="17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="C46" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="B47" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B51" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C51" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+    <row r="52" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B52" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C52" s="18" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>57</v>
+      <c r="A55" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>60</v>
+      <c r="A56" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="C62" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="B63" s="17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="61" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
+      <c r="C63" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="C64" s="18" t="s">
         <v>75</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="21" t="s">
-        <v>92</v>
+      <c r="A67" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="22" t="s">
-        <v>95</v>
+      <c r="A68" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
-        <v>104</v>
+      <c r="A71" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
-        <v>107</v>
+      <c r="A72" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B79" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="C79" s="18" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="21" t="s">
+    <row r="80" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B80" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C80" s="18" t="s">
         <v>124</v>
       </c>
     </row>
+    <row r="81" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="28">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
@@ -2054,7 +2207,10 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2078,126 +2234,126 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B3" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="25" t="s">
         <v>134</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>131</v>
       </c>
       <c r="D3" s="25">
         <v>2</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D4" s="24">
         <v>5</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" s="25">
         <v>3</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D7" s="25">
         <v>1</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2206,7 +2362,7 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -2215,7 +2371,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2224,7 +2380,7 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2245,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2253,117 +2409,322 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2395,60 +2756,60 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K1" s="27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L1" s="27" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="F2" s="30">
         <v>799</v>
@@ -2472,24 +2833,24 @@
         <v>8</v>
       </c>
       <c r="M2" s="29" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="F3" s="33">
         <v>1599</v>
@@ -2513,24 +2874,24 @@
         <v>4</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="F4" s="30">
         <v>499</v>
@@ -2554,7 +2915,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2563,8 +2924,8 @@
     <dataValidation type="list" showInputMessage="1" promptTitle="Brand Type" prompt="Generic or Branded. Branded auth documents are uploaded separately, not in Excel." showErrorMessage="1" errorTitle="Brand Type" error="Pick one of: Generic, Branded" sqref="B2:B200">
       <formula1>"Generic,Branded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Size" prompt="Pick a size from the list. For multiple sizes add more names separated by comma (example: 6, 7, 8)." errorTitle="Size" error="Pick a size from the Size dropdown (admin Size attributes)." sqref="E2:E200">
-      <formula1>'Size Names'!$A$2:$A$23</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Size" prompt="Pick one size from the list. Kids Fashion: choose an age-group size (6-9 Months, 12-15 Months, 2-2.5 Years), not adult S/M/L." showErrorMessage="1" errorTitle="Size" error="Pick one size from the Size dropdown (admin Size attributes)." sqref="E2:E200">
+      <formula1>'Size Names'!$A$2:$A$64</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2609,111 +2970,111 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K1" s="27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L1" s="27" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AA1" s="35" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AB1" s="35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AC1" s="35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="F2" s="30">
         <v>799</v>
@@ -2737,55 +3098,55 @@
         <v>8</v>
       </c>
       <c r="M2" s="29" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="N2" s="29" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="O2" s="29" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="P2" s="29" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="Q2" s="29" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="S2" s="31">
         <v>12</v>
       </c>
       <c r="T2" s="29" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="U2" s="29" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="V2" s="38" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="W2" s="38" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="Y2" s="38" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="Z2" s="38" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="AA2" s="29" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="AB2" s="38" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="AC2" s="29" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="AD2" s="29">
         <v>5</v>
@@ -2793,19 +3154,19 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="F3" s="33">
         <v>1599</v>
@@ -2829,55 +3190,55 @@
         <v>4</v>
       </c>
       <c r="M3" s="32" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="N3" s="32" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="R3" s="32" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="S3" s="34">
         <v>18</v>
       </c>
       <c r="T3" s="32" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="U3" s="32" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="V3" s="39" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="W3" s="39" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="X3" s="39" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="Y3" s="39" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="Z3" s="39" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="AA3" s="32" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="AB3" s="39" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="AC3" s="32" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="AD3" s="32">
         <v>3</v>
@@ -2885,19 +3246,19 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="F4" s="30">
         <v>499</v>
@@ -2921,55 +3282,55 @@
         <v>3</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="O4" s="29" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="P4" s="29" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="Q4" s="29" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="S4" s="31">
         <v>5</v>
       </c>
       <c r="T4" s="29" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="U4" s="29" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="V4" s="38" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="W4" s="38" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="X4" s="38" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="Z4" s="38" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="AA4" s="29" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="AB4" s="38" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="AC4" s="29" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="AD4" s="29">
         <v>4</v>
